--- a/docs/Projects-Site.xlsx
+++ b/docs/Projects-Site.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D Drive\MyProjects\Evolve\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D Drive\MyProjects\evolve\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{147DA118-35C7-4153-B5DB-272C973BC890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{225175D4-4FD9-43B4-9C51-7D1D3CF7325C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{FFE9247F-1A95-44C9-8EB0-8DA88F9A0E5F}"/>
   </bookViews>
@@ -297,7 +297,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mmm\-yyyy"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -326,6 +326,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -379,7 +387,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -394,6 +402,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -769,16 +778,16 @@
       <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="2">
         <v>33939</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="2">
         <v>34028</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="10" t="s">
         <v>70</v>
       </c>
       <c r="G2" s="8" t="s">
@@ -815,16 +824,16 @@
       <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="2">
         <v>34304</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="2">
         <v>34485</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="10" t="s">
         <v>71</v>
       </c>
       <c r="G4" s="8" t="s">
@@ -861,16 +870,16 @@
       <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="2">
         <v>34881</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="2">
         <v>35033</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="10" t="s">
         <v>72</v>
       </c>
       <c r="G6" s="8" t="s">
@@ -999,16 +1008,16 @@
       <c r="B12" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="2">
         <v>36008</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="2">
         <v>36191</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="10" t="s">
         <v>73</v>
       </c>
       <c r="G12" s="8" t="s">
@@ -1045,16 +1054,16 @@
       <c r="B14" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="2">
         <v>36161</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="2">
         <v>36219</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="10" t="s">
         <v>74</v>
       </c>
       <c r="G14" s="8" t="s">
@@ -1114,16 +1123,16 @@
       <c r="B17" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="2">
         <v>36161</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="2">
         <v>36677</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="10" t="s">
         <v>75</v>
       </c>
       <c r="G17" s="8" t="s">
@@ -1206,16 +1215,16 @@
       <c r="B21" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="2">
         <v>37104</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D21" s="2">
         <v>37315</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="E21" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="F21" s="10" t="s">
         <v>58</v>
       </c>
       <c r="G21" s="8" t="s">
@@ -1229,16 +1238,16 @@
       <c r="B22" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22" s="2">
         <v>37316</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="2">
         <v>37499</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="E22" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="F22" s="10" t="s">
         <v>76</v>
       </c>
       <c r="G22" s="8" t="s">
@@ -1321,16 +1330,16 @@
       <c r="B26" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C26" s="2">
         <v>38869</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D26" s="2">
         <v>39051</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="F26" s="10" t="s">
         <v>61</v>
       </c>
       <c r="G26" s="8" t="s">
@@ -1802,5 +1811,6 @@
     <hyperlink ref="B12" r:id="rId1" display="http://www.ril.com/" xr:uid="{7645A6E2-9A24-4E4B-A804-CD4EEBAA8AF1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>